--- a/APIs/HMS/HMS/Uploads/1/c328bd23-b934-4b75-95c7-5772158ce774.xlsx
+++ b/APIs/HMS/HMS/Uploads/1/c328bd23-b934-4b75-95c7-5772158ce774.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HMS\Code\APIs\HMS\HMS\Uploads\1\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -957,7 +957,7 @@
     <t>ELMTA7834K</t>
   </si>
   <si>
-    <t>AG021</t>
+    <t>AG022</t>
   </si>
 </sst>
 </file>
@@ -1749,7 +1749,7 @@
         <v>164</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y2" s="2">
         <v>40605</v>
@@ -2057,7 +2057,7 @@
         <v>165</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y3" s="2">
         <v>42594</v>
@@ -2362,7 +2362,7 @@
         <v>166</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y4" s="2">
         <v>38373</v>
@@ -2667,7 +2667,7 @@
         <v>167</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y5" s="2">
         <v>43084</v>
@@ -2972,7 +2972,7 @@
         <v>168</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y6" s="2">
         <v>40686</v>
